--- a/stage/transform/files/reference/dim_conta_cc.xlsx
+++ b/stage/transform/files/reference/dim_conta_cc.xlsx
@@ -12,6 +12,9 @@
     <sheet name="tipos_documento" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="instrucoes" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">conta_cc!$A$1:$K$306</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -22,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="753">
   <si>
     <t xml:space="preserve">empresa_cod</t>
   </si>
@@ -2307,7 +2310,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2349,6 +2352,11 @@
       <name val="Courier New"/>
       <family val="3"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -2459,7 +2467,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2492,7 +2500,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2500,7 +2512,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2516,7 +2528,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2533,11 +2545,27 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF595959"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2552,7 +2580,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FF1F4E79"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF375623"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2619,6 +2655,10 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2902,7 +2942,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="n">
         <v>17</v>
       </c>
@@ -2952,7 +2992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>21</v>
       </c>
@@ -2977,7 +3017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>22</v>
       </c>
@@ -3002,7 +3042,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>20</v>
       </c>
@@ -3027,7 +3067,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>21</v>
       </c>
@@ -3052,7 +3092,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>20</v>
       </c>
@@ -3102,7 +3142,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>18</v>
       </c>
@@ -3127,7 +3167,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>1</v>
       </c>
@@ -3158,7 +3198,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>19</v>
       </c>
@@ -3183,7 +3223,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>1</v>
       </c>
@@ -3208,7 +3248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>1</v>
       </c>
@@ -3233,7 +3273,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
@@ -3258,7 +3298,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>1</v>
       </c>
@@ -3283,7 +3323,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>11</v>
       </c>
@@ -3308,7 +3348,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>36</v>
       </c>
@@ -3333,7 +3373,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>1</v>
       </c>
@@ -3364,7 +3404,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>1</v>
       </c>
@@ -3395,7 +3435,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>1</v>
       </c>
@@ -3426,7 +3466,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>22</v>
       </c>
@@ -3451,7 +3491,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
@@ -3476,7 +3516,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>20</v>
       </c>
@@ -3501,7 +3541,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>18</v>
       </c>
@@ -3526,7 +3566,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>19</v>
       </c>
@@ -3551,7 +3591,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>1</v>
       </c>
@@ -3584,7 +3624,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>1</v>
       </c>
@@ -3615,7 +3655,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>23</v>
       </c>
@@ -3640,7 +3680,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>24</v>
       </c>
@@ -3690,7 +3730,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>1</v>
       </c>
@@ -3721,7 +3761,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>1</v>
       </c>
@@ -3752,7 +3792,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>38</v>
       </c>
@@ -3777,7 +3817,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
         <v>23</v>
       </c>
@@ -3974,7 +4014,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
         <v>1</v>
       </c>
@@ -4005,7 +4045,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
         <v>24</v>
       </c>
@@ -4030,7 +4070,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>29</v>
       </c>
@@ -4080,7 +4120,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>34</v>
       </c>
@@ -4105,7 +4145,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>32</v>
       </c>
@@ -4180,7 +4220,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
         <v>1</v>
       </c>
@@ -4205,7 +4245,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
         <v>28</v>
       </c>
@@ -4255,7 +4295,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>30</v>
       </c>
@@ -4280,7 +4320,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
         <v>1</v>
       </c>
@@ -4336,7 +4376,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
         <v>27</v>
       </c>
@@ -4361,7 +4401,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
         <v>27</v>
       </c>
@@ -4386,7 +4426,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
         <v>27</v>
       </c>
@@ -4411,7 +4451,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="n">
         <v>4</v>
       </c>
@@ -4436,7 +4476,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
         <v>27</v>
       </c>
@@ -4461,7 +4501,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
         <v>27</v>
       </c>
@@ -4486,7 +4526,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="n">
         <v>27</v>
       </c>
@@ -4511,7 +4551,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
         <v>35</v>
       </c>
@@ -4536,7 +4576,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
         <v>1</v>
       </c>
@@ -4586,7 +4626,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
         <v>37</v>
       </c>
@@ -4611,7 +4651,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
         <v>37</v>
       </c>
@@ -4636,7 +4676,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
         <v>38</v>
       </c>
@@ -4661,7 +4701,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
         <v>39</v>
       </c>
@@ -4686,7 +4726,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
         <v>40</v>
       </c>
@@ -4711,7 +4751,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>1</v>
       </c>
@@ -4736,7 +4776,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>37</v>
       </c>
@@ -4761,7 +4801,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>41</v>
       </c>
@@ -4786,7 +4826,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>37</v>
       </c>
@@ -4811,7 +4851,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>37</v>
       </c>
@@ -4836,7 +4876,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>43</v>
       </c>
@@ -4861,7 +4901,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
         <v>42</v>
       </c>
@@ -4886,7 +4926,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>3</v>
       </c>
@@ -4911,7 +4951,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="n">
         <v>37</v>
       </c>
@@ -4936,7 +4976,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
         <v>37</v>
       </c>
@@ -4961,7 +5001,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="n">
         <v>37</v>
       </c>
@@ -4986,7 +5026,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>37</v>
       </c>
@@ -5011,7 +5051,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
         <v>3</v>
       </c>
@@ -5036,7 +5076,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>48</v>
       </c>
@@ -5061,7 +5101,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>1</v>
       </c>
@@ -5086,7 +5126,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>37</v>
       </c>
@@ -5111,7 +5151,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
         <v>49</v>
       </c>
@@ -5136,7 +5176,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>37</v>
       </c>
@@ -5161,7 +5201,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
         <v>37</v>
       </c>
@@ -5279,7 +5319,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="n">
         <v>55</v>
       </c>
@@ -5304,7 +5344,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
         <v>54</v>
       </c>
@@ -5329,7 +5369,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
         <v>53</v>
       </c>
@@ -5354,7 +5394,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
         <v>52</v>
       </c>
@@ -5379,7 +5419,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="n">
         <v>51</v>
       </c>
@@ -5404,7 +5444,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
         <v>32</v>
       </c>
@@ -5429,7 +5469,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
         <v>59</v>
       </c>
@@ -5454,7 +5494,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>61</v>
       </c>
@@ -5479,7 +5519,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="n">
         <v>62</v>
       </c>
@@ -5504,7 +5544,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
         <v>63</v>
       </c>
@@ -5529,7 +5569,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="n">
         <v>37</v>
       </c>
@@ -5554,7 +5594,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
         <v>1</v>
       </c>
@@ -5579,7 +5619,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="n">
         <v>64</v>
       </c>
@@ -5604,7 +5644,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="n">
         <v>66</v>
       </c>
@@ -5629,7 +5669,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="n">
         <v>17</v>
       </c>
@@ -5754,7 +5794,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="n">
         <v>18</v>
       </c>
@@ -5779,7 +5819,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="n">
         <v>1</v>
       </c>
@@ -5810,7 +5850,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="n">
         <v>29</v>
       </c>
@@ -5860,7 +5900,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="n">
         <v>24</v>
       </c>
@@ -5885,7 +5925,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="n">
         <v>25</v>
       </c>
@@ -5941,7 +5981,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="n">
         <v>1</v>
       </c>
@@ -5972,7 +6012,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="n">
         <v>34</v>
       </c>
@@ -5997,7 +6037,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="18" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="n">
         <v>32</v>
       </c>
@@ -9825,7 +9865,9 @@
       <c r="D254" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="E254" s="5"/>
+      <c r="E254" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="F254" s="6"/>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
@@ -11214,29 +11256,30 @@
       </c>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="8" t="s">
+      <c r="A308" s="9" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="9"/>
-      <c r="B309" s="10" t="s">
+      <c r="A309" s="10"/>
+      <c r="B309" s="11" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="11"/>
-      <c r="B310" s="10" t="s">
+      <c r="A310" s="12"/>
+      <c r="B310" s="11" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="12"/>
-      <c r="B311" s="10" t="s">
+      <c r="A311" s="13"/>
+      <c r="B311" s="11" t="s">
         <v>696</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K306"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -11244,6 +11287,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11264,177 +11308,177 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>707</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="14" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="14" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="14" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="14" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="14" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="14" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="14" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="14" t="s">
         <v>721</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="14" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="14" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="14" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="14" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="14" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="14" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="14" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="14" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="14" t="s">
         <v>730</v>
       </c>
     </row>
@@ -11463,12 +11507,12 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>731</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -11485,100 +11529,100 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>736</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>737</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>738</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>740</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>741</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>743</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>744</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>743</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>746</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>743</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>748</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>743</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>750</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>737</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>751</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>752</v>
       </c>
     </row>

--- a/stage/transform/files/reference/dim_conta_cc.xlsx
+++ b/stage/transform/files/reference/dim_conta_cc.xlsx
@@ -13,7 +13,7 @@
     <sheet name="instrucoes" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">conta_cc!$A$1:$K$306</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">conta_cc!$A$1:$K$328</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="777">
   <si>
     <t xml:space="preserve">empresa_cod</t>
   </si>
@@ -536,6 +536,9 @@
     <t xml:space="preserve">1150</t>
   </si>
   <si>
+    <t xml:space="preserve">RESIDENCIAL ROSA DA FONSECA III</t>
+  </si>
+  <si>
     <t xml:space="preserve">RESIDENCIAL MANOEL ALVES DE FRANÇA II - INCORPORAÇÃO</t>
   </si>
   <si>
@@ -2123,16 +2126,85 @@
     <t xml:space="preserve">99993</t>
   </si>
   <si>
-    <t xml:space="preserve">Legenda:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colunas de contexto — não altere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colunas para preencher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chave gerada automaticamente — não altere</t>
+    <t xml:space="preserve">SPLENDIDO RESIDENCE – COMERCIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. B. FORTEMIX CONCRETO LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMINISTRATIVO RB FORTEMIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGB ADMINISTRADORA DE BENS LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGB ADMINISTRADORA DE BENS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELESIL PROJETO 01 EMPREENDIMENTO IMOBILIARIO SPE LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONNECTION WORK AND LIFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRECHES CRIA 2024 - SCP02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRECHES CRIA 2024 - SCP02 - TELESIL ENGENHARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUO RESIDENCE - PROJETOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRUTA FENIX EMPREENDIMENTO IMOBILIARIO SPE LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRUTA FENIX - INCORPORAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB2 PARTICIPACOES LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB2 PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELESIL ENGENHARIA LTDA - RESIDENCIAL RESERVA DAS ARVORES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESERVA DAS ARVORES - ASSISTENCIA TÉCNICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELESIL ENGENHARIA LTDA - RESIDENCIAL COSTA AZUL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESIDENCIAL COSTA AZUL - INCORPORAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELESIL ENGENHARIA LTDA - RESID. COMEND. GUTTENBERG BREDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELESIL ENGENHARIA LTDA - FILIAL SUL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESIDENCIAL MITRA - INCORPORAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINALIZAÇÃO VIÁRIA NA RUA JOÃO SCHARDONG - TELESIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITGES II EMPREENDIMENTO IMOBILIARIO SPE LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITGES II - PROJETOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESIDENCIAL MANOEL ALVES DE FRANÇA III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSÓRCIO PMCMV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUME - OBRA</t>
   </si>
   <si>
     <t xml:space="preserve">documento</t>
@@ -2310,7 +2382,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2351,24 +2423,6 @@
       <sz val="9"/>
       <name val="Courier New"/>
       <family val="3"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2467,7 +2521,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2500,35 +2554,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2841,11 +2871,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K311"/>
+  <dimension ref="A1:K328"/>
   <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="72.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="102.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
@@ -4509,7 +4539,7 @@
         <v>152</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1151</v>
+        <v>150</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>164</v>
@@ -4522,8 +4552,8 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="7" t="s">
-        <v>165</v>
+      <c r="K63" s="5" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4534,10 +4564,10 @@
         <v>152</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>1152</v>
+        <v>149</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>13</v>
@@ -4547,22 +4577,22 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
-      <c r="K64" s="7" t="s">
-        <v>167</v>
+      <c r="K64" s="5" t="n">
+        <v>149</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1158</v>
+        <v>1151</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>13</v>
@@ -4573,24 +4603,24 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
       <c r="K65" s="7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
@@ -4598,21 +4628,21 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
       <c r="K66" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>116</v>
+        <v>1158</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>13</v>
@@ -4623,24 +4653,24 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
       <c r="K67" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
@@ -4648,24 +4678,24 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
       <c r="K68" s="7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1164</v>
+        <v>116</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
@@ -4673,24 +4703,24 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
       <c r="K69" s="7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
@@ -4698,24 +4728,24 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -4723,21 +4753,21 @@
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
       <c r="K71" s="7" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>13</v>
@@ -4748,24 +4778,24 @@
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
       <c r="K72" s="7" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>11</v>
+        <v>184</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>117</v>
+        <v>1167</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
@@ -4773,24 +4803,24 @@
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
       <c r="K73" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
@@ -4798,24 +4828,24 @@
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
       <c r="K74" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>1172</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
@@ -4823,7 +4853,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
       <c r="K75" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4831,16 +4861,16 @@
         <v>37</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
@@ -4848,24 +4878,24 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
       <c r="K76" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
@@ -4873,24 +4903,24 @@
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
       <c r="K77" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
@@ -4898,24 +4928,24 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
       <c r="K78" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
@@ -4923,21 +4953,21 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
       <c r="K79" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>118</v>
+        <v>1177</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>13</v>
@@ -4948,24 +4978,24 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
       <c r="K80" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
@@ -4973,24 +5003,24 @@
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
       <c r="K81" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>1183</v>
+        <v>118</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
@@ -4998,7 +5028,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
       <c r="K82" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5006,16 +5036,16 @@
         <v>37</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
@@ -5023,7 +5053,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
       <c r="K83" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5031,16 +5061,16 @@
         <v>37</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
@@ -5048,24 +5078,24 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
       <c r="K84" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>119</v>
+        <v>1186</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
@@ -5073,24 +5103,24 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
       <c r="K85" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
@@ -5098,24 +5128,24 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
       <c r="K86" s="7" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>11</v>
+        <v>207</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1191</v>
+        <v>119</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
@@ -5123,24 +5153,24 @@
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
       <c r="K87" s="7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
@@ -5148,24 +5178,24 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
       <c r="K88" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>226</v>
+        <v>11</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
@@ -5173,7 +5203,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="6"/>
       <c r="K89" s="7" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5181,16 +5211,16 @@
         <v>37</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
@@ -5198,24 +5228,24 @@
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
       <c r="K90" s="7" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>176</v>
+        <v>227</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
@@ -5223,69 +5253,57 @@
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
       <c r="K91" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>120</v>
+        <v>1196</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F92" s="6"/>
-      <c r="G92" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
       <c r="I92" s="6"/>
-      <c r="J92" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J92" s="6"/>
       <c r="K92" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>120</v>
+        <v>1198</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>43</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
-      <c r="K93" s="5" t="s">
-        <v>236</v>
+      <c r="K93" s="7" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5299,88 +5317,100 @@
         <v>120</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>110</v>
-      </c>
+      <c r="F94" s="6"/>
       <c r="G94" s="6" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="5" t="s">
-        <v>237</v>
+      <c r="J94" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>238</v>
+        <v>11</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
+      <c r="F95" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
-      <c r="K95" s="7" t="s">
-        <v>240</v>
+      <c r="K95" s="5" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>241</v>
+        <v>11</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>1201</v>
+        <v>120</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
+      <c r="F96" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
-      <c r="K96" s="7" t="s">
-        <v>243</v>
+      <c r="K96" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>13</v>
@@ -5391,21 +5421,21 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
       <c r="K97" s="7" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>13</v>
@@ -5416,21 +5446,21 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
       <c r="K98" s="7" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>13</v>
@@ -5441,21 +5471,21 @@
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
       <c r="K99" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>131</v>
+        <v>248</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>13</v>
@@ -5466,21 +5496,21 @@
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
       <c r="K100" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>13</v>
@@ -5491,21 +5521,21 @@
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
       <c r="K101" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>13</v>
@@ -5516,21 +5546,21 @@
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
       <c r="K102" s="7" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>13</v>
@@ -5541,21 +5571,21 @@
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
       <c r="K103" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>13</v>
@@ -5566,24 +5596,24 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
       <c r="K104" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
@@ -5591,24 +5621,24 @@
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
       <c r="K105" s="7" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>11</v>
+        <v>265</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
@@ -5616,24 +5646,24 @@
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
       <c r="K106" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>271</v>
+        <v>177</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
@@ -5641,24 +5671,24 @@
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
       <c r="K107" s="7" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>274</v>
+        <v>11</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
@@ -5666,21 +5696,21 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
       <c r="K108" s="7" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="n">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>123</v>
+        <v>1214</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>13</v>
@@ -5691,21 +5721,21 @@
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
       <c r="K109" s="7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>11</v>
+        <v>275</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>124</v>
+        <v>1215</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>13</v>
@@ -5716,21 +5746,21 @@
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
       <c r="K110" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>13</v>
@@ -5741,7 +5771,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
       <c r="K111" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5752,10 +5782,10 @@
         <v>11</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E112" s="5" t="s">
         <v>13</v>
@@ -5766,7 +5796,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
       <c r="K112" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5777,10 +5807,10 @@
         <v>11</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>13</v>
@@ -5791,21 +5821,21 @@
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
       <c r="K113" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>13</v>
@@ -5816,7 +5846,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
       <c r="K114" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5827,41 +5857,35 @@
         <v>11</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F115" s="6"/>
-      <c r="G115" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
       <c r="I115" s="6"/>
-      <c r="J115" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J115" s="6"/>
       <c r="K115" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>13</v>
@@ -5872,7 +5896,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
       <c r="K116" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5883,35 +5907,41 @@
         <v>11</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1300</v>
+        <v>129</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
+      <c r="G117" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
+      <c r="J117" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K117" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>13</v>
@@ -5922,21 +5952,21 @@
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
       <c r="K118" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>297</v>
+        <v>11</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>132</v>
+        <v>1300</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>13</v>
@@ -5947,133 +5977,133 @@
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
       <c r="K119" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F120" s="6"/>
-      <c r="G120" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
       <c r="I120" s="6"/>
-      <c r="J120" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J120" s="6"/>
       <c r="K120" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>11</v>
+        <v>298</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F121" s="6"/>
-      <c r="G121" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G121" s="6"/>
+      <c r="H121" s="6"/>
       <c r="I121" s="6"/>
-      <c r="J121" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J121" s="6"/>
       <c r="K121" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
+      <c r="G122" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
+      <c r="J122" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K122" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
+      <c r="G123" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
+      <c r="J123" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K123" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>13</v>
@@ -6084,21 +6114,21 @@
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
       <c r="K124" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>13</v>
@@ -6109,21 +6139,21 @@
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
       <c r="K125" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>13</v>
@@ -6134,7 +6164,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
       <c r="K126" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6145,58 +6175,46 @@
         <v>11</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F127" s="6"/>
-      <c r="G127" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
       <c r="I127" s="6"/>
-      <c r="J127" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J127" s="6"/>
       <c r="K127" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F128" s="6"/>
-      <c r="G128" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
       <c r="I128" s="6"/>
-      <c r="J128" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J128" s="6"/>
       <c r="K128" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6207,21 +6225,27 @@
         <v>11</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
+      <c r="G129" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
+      <c r="J129" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K129" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6232,38 +6256,44 @@
         <v>11</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
+      <c r="G130" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
+      <c r="J130" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K130" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
@@ -6271,21 +6301,21 @@
       <c r="I131" s="6"/>
       <c r="J131" s="6"/>
       <c r="K131" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>13</v>
@@ -6296,73 +6326,57 @@
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
       <c r="K132" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>325</v>
+        <v>152</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F133" s="6"/>
-      <c r="G133" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I133" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6"/>
       <c r="K133" s="7" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B134" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="7" t="s">
         <v>325</v>
-      </c>
-      <c r="C134" s="5" t="n">
-        <v>1482</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K134" s="7" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6370,13 +6384,13 @@
         <v>26</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1483</v>
+        <v>148</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>41</v>
@@ -6389,13 +6403,13 @@
         <v>43</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J135" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6403,13 +6417,13 @@
         <v>26</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>41</v>
@@ -6422,13 +6436,13 @@
         <v>43</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J136" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6436,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>41</v>
@@ -6455,13 +6469,13 @@
         <v>43</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J137" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6469,13 +6483,13 @@
         <v>26</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>41</v>
@@ -6488,58 +6502,60 @@
         <v>43</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J138" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>11</v>
+        <v>326</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>15</v>
+        <v>1485</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" s="6" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I139" s="6"/>
+      <c r="I139" s="6" t="s">
+        <v>328</v>
+      </c>
       <c r="J139" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>11</v>
+        <v>326</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>153</v>
+        <v>1486</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>41</v>
@@ -6551,140 +6567,142 @@
       <c r="H140" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I140" s="6"/>
+      <c r="I140" s="6" t="s">
+        <v>328</v>
+      </c>
       <c r="J140" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>343</v>
+        <v>11</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F141" s="6"/>
       <c r="G141" s="6" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="H141" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I141" s="6" t="s">
-        <v>345</v>
-      </c>
+      <c r="I141" s="6"/>
       <c r="J141" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>343</v>
+        <v>11</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>1541</v>
+        <v>153</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H142" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I142" s="6" t="s">
-        <v>345</v>
-      </c>
+      <c r="I142" s="6"/>
       <c r="J142" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>11</v>
+        <v>344</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F143" s="6"/>
       <c r="G143" s="6" t="s">
-        <v>350</v>
+        <v>98</v>
       </c>
       <c r="H143" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I143" s="6"/>
+      <c r="I143" s="6" t="s">
+        <v>346</v>
+      </c>
       <c r="J143" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>11</v>
+        <v>344</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>156</v>
+        <v>1541</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F144" s="6"/>
       <c r="G144" s="6" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I144" s="6"/>
+      <c r="I144" s="6" t="s">
+        <v>346</v>
+      </c>
       <c r="J144" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6695,17 +6713,17 @@
         <v>11</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F145" s="6"/>
       <c r="G145" s="6" t="s">
-        <v>42</v>
+        <v>351</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>43</v>
@@ -6715,32 +6733,38 @@
         <v>44</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="5" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
+      <c r="G146" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
+      <c r="J146" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K146" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6751,69 +6775,69 @@
         <v>11</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
+      <c r="G147" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H147" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
+      <c r="J147" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K147" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="5" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F148" s="6"/>
-      <c r="G148" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G148" s="6"/>
+      <c r="H148" s="6"/>
       <c r="I148" s="6"/>
-      <c r="J148" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J148" s="6"/>
       <c r="K148" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
@@ -6821,7 +6845,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
       <c r="K149" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6832,17 +6856,17 @@
         <v>11</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F150" s="6"/>
       <c r="G150" s="6" t="s">
-        <v>365</v>
+        <v>42</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>43</v>
@@ -6852,24 +6876,24 @@
         <v>44</v>
       </c>
       <c r="K150" s="7" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
@@ -6877,49 +6901,55 @@
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
       <c r="K151" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="5" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
+      <c r="G152" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
+      <c r="J152" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K152" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
@@ -6927,21 +6957,21 @@
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
       <c r="K153" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="5" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>13</v>
@@ -6952,24 +6982,24 @@
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
       <c r="K154" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
@@ -6977,24 +7007,24 @@
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
       <c r="K155" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
@@ -7002,24 +7032,24 @@
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
       <c r="K156" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
@@ -7027,24 +7057,24 @@
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
       <c r="K157" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
@@ -7052,73 +7082,57 @@
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
       <c r="K158" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>383</v>
+        <v>177</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="F159" s="6"/>
-      <c r="G159" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="H159" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I159" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="J159" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="G159" s="6"/>
+      <c r="H159" s="6"/>
+      <c r="I159" s="6"/>
+      <c r="J159" s="6"/>
       <c r="K159" s="7" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="5" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>383</v>
+        <v>11</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>1801</v>
+        <v>179</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E160" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F160" s="6"/>
-      <c r="G160" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I160" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="J160" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="G160" s="6"/>
+      <c r="H160" s="6"/>
+      <c r="I160" s="6"/>
+      <c r="J160" s="6"/>
       <c r="K160" s="7" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7126,32 +7140,32 @@
         <v>46</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>18011</v>
+        <v>180</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E161" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H161" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J161" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7159,32 +7173,32 @@
         <v>46</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>18012</v>
+        <v>1801</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E162" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F162" s="6"/>
       <c r="G162" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H162" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J162" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K162" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7192,32 +7206,32 @@
         <v>46</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>18013</v>
+        <v>18011</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E163" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J163" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7225,32 +7239,32 @@
         <v>46</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>18014</v>
+        <v>18012</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E164" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F164" s="6"/>
       <c r="G164" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H164" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J164" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K164" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7258,32 +7272,32 @@
         <v>46</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>1803</v>
+        <v>18013</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E165" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F165" s="6"/>
       <c r="G165" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H165" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J165" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7291,32 +7305,32 @@
         <v>46</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>18031</v>
+        <v>18014</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H166" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J166" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K166" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7324,32 +7338,32 @@
         <v>46</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>18032</v>
+        <v>1803</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E167" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J167" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K167" s="7" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7357,32 +7371,32 @@
         <v>46</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>18033</v>
+        <v>18031</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J168" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K168" s="7" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7390,32 +7404,32 @@
         <v>46</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>18034</v>
+        <v>18032</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E169" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F169" s="6"/>
       <c r="G169" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J169" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K169" s="7" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7423,32 +7437,32 @@
         <v>46</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>18035</v>
+        <v>18033</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E170" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F170" s="6"/>
       <c r="G170" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J170" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K170" s="7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7456,32 +7470,32 @@
         <v>46</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>1804</v>
+        <v>18034</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E171" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F171" s="6"/>
       <c r="G171" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J171" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K171" s="7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7489,32 +7503,32 @@
         <v>46</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>18041</v>
+        <v>18035</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E172" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F172" s="6"/>
       <c r="G172" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H172" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J172" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K172" s="7" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7522,32 +7536,32 @@
         <v>46</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>18042</v>
+        <v>1804</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E173" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J173" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7555,32 +7569,32 @@
         <v>46</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>18043</v>
+        <v>18041</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E174" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H174" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J174" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K174" s="7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7588,32 +7602,32 @@
         <v>46</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>18044</v>
+        <v>18042</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E175" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H175" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J175" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K175" s="7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7621,32 +7635,32 @@
         <v>46</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>18045</v>
+        <v>18043</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E176" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H176" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J176" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K176" s="7" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7654,32 +7668,32 @@
         <v>46</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>1805</v>
+        <v>18044</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E177" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H177" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J177" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K177" s="7" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7687,32 +7701,32 @@
         <v>46</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>18051</v>
+        <v>18045</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E178" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H178" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J178" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K178" s="7" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7720,32 +7734,32 @@
         <v>46</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>18052</v>
+        <v>1805</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E179" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F179" s="6"/>
       <c r="G179" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H179" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J179" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K179" s="7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7753,32 +7767,32 @@
         <v>46</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>18053</v>
+        <v>18051</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H180" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J180" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K180" s="7" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7786,32 +7800,32 @@
         <v>46</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>18054</v>
+        <v>18052</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E181" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H181" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J181" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K181" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7819,32 +7833,32 @@
         <v>46</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>18055</v>
+        <v>18053</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E182" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F182" s="6"/>
       <c r="G182" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H182" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J182" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K182" s="7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7852,32 +7866,32 @@
         <v>46</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>1806</v>
+        <v>18054</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E183" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F183" s="6"/>
       <c r="G183" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H183" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J183" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K183" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7885,32 +7899,32 @@
         <v>46</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>18061</v>
+        <v>18055</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E184" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F184" s="6"/>
       <c r="G184" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H184" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J184" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K184" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7918,32 +7932,32 @@
         <v>46</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>18062</v>
+        <v>1806</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E185" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F185" s="6"/>
       <c r="G185" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H185" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J185" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K185" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7951,32 +7965,32 @@
         <v>46</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>18063</v>
+        <v>18061</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E186" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F186" s="6"/>
       <c r="G186" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H186" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J186" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K186" s="7" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7984,32 +7998,32 @@
         <v>46</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>18064</v>
+        <v>18062</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E187" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H187" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J187" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K187" s="7" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8017,32 +8031,32 @@
         <v>46</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>18065</v>
+        <v>18063</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E188" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F188" s="6"/>
       <c r="G188" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H188" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J188" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K188" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8050,32 +8064,32 @@
         <v>46</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>18066</v>
+        <v>18064</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E189" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F189" s="6"/>
       <c r="G189" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H189" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J189" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K189" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8083,32 +8097,32 @@
         <v>46</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>18067</v>
+        <v>18065</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E190" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F190" s="6"/>
       <c r="G190" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H190" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J190" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K190" s="7" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8116,32 +8130,32 @@
         <v>46</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>18068</v>
+        <v>18066</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E191" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F191" s="6"/>
       <c r="G191" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H191" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J191" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K191" s="7" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8149,32 +8163,32 @@
         <v>46</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>1807</v>
+        <v>18067</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E192" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H192" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J192" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K192" s="7" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8182,32 +8196,32 @@
         <v>46</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>18071</v>
+        <v>18068</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F193" s="6"/>
       <c r="G193" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H193" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I193" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J193" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K193" s="7" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8215,32 +8229,32 @@
         <v>46</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>18072</v>
+        <v>1807</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E194" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F194" s="6"/>
       <c r="G194" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H194" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J194" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K194" s="7" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8248,32 +8262,32 @@
         <v>46</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C195" s="5" t="n">
-        <v>18073</v>
+        <v>18071</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E195" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F195" s="6"/>
       <c r="G195" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H195" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J195" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K195" s="7" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8281,32 +8295,32 @@
         <v>46</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>18074</v>
+        <v>18072</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E196" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F196" s="6"/>
       <c r="G196" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H196" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J196" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K196" s="7" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8314,32 +8328,32 @@
         <v>46</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>18075</v>
+        <v>18073</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E197" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F197" s="6"/>
       <c r="G197" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H197" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I197" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J197" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K197" s="7" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8347,32 +8361,32 @@
         <v>46</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>1808</v>
+        <v>18074</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E198" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F198" s="6"/>
       <c r="G198" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H198" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I198" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J198" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K198" s="7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8380,32 +8394,32 @@
         <v>46</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>18081</v>
+        <v>18075</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E199" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F199" s="6"/>
       <c r="G199" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H199" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I199" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J199" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K199" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8413,32 +8427,32 @@
         <v>46</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>18082</v>
+        <v>1808</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E200" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F200" s="6"/>
       <c r="G200" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H200" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I200" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J200" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K200" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8446,32 +8460,32 @@
         <v>46</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>18083</v>
+        <v>18081</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F201" s="6"/>
       <c r="G201" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H201" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I201" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J201" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K201" s="7" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8479,32 +8493,32 @@
         <v>46</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>18084</v>
+        <v>18082</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E202" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F202" s="6"/>
       <c r="G202" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H202" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I202" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J202" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K202" s="7" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8512,32 +8526,32 @@
         <v>46</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>18085</v>
+        <v>18083</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F203" s="6"/>
       <c r="G203" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H203" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I203" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J203" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K203" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8545,32 +8559,32 @@
         <v>46</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>18086</v>
+        <v>18084</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E204" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F204" s="6"/>
       <c r="G204" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H204" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I204" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J204" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K204" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8578,88 +8592,98 @@
         <v>46</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>18087</v>
+        <v>18085</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F205" s="6"/>
       <c r="G205" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H205" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J205" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K205" s="7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="5" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>11</v>
+        <v>384</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>1809</v>
+        <v>18086</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E206" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F206" s="6"/>
       <c r="G206" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H206" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I206" s="6"/>
+      <c r="I206" s="6" t="s">
+        <v>387</v>
+      </c>
       <c r="J206" s="6" t="s">
         <v>44</v>
       </c>
       <c r="K206" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>482</v>
+        <v>384</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>181</v>
+        <v>18087</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
-      <c r="J207" s="6"/>
+      <c r="G207" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="H207" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I207" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="J207" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K207" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8670,69 +8694,69 @@
         <v>11</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>184</v>
+        <v>1809</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F208" s="6"/>
-      <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
+      <c r="G208" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="H208" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I208" s="6"/>
-      <c r="J208" s="6"/>
+      <c r="J208" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K208" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>11</v>
+        <v>483</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E209" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F209" s="6"/>
-      <c r="G209" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H209" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G209" s="6"/>
+      <c r="H209" s="6"/>
       <c r="I209" s="6"/>
-      <c r="J209" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J209" s="6"/>
       <c r="K209" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
@@ -8740,49 +8764,55 @@
       <c r="I210" s="6"/>
       <c r="J210" s="6"/>
       <c r="K210" s="7" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>219</v>
+        <v>11</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E211" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F211" s="6"/>
-      <c r="G211" s="6"/>
-      <c r="H211" s="6"/>
+      <c r="G211" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H211" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I211" s="6"/>
-      <c r="J211" s="6"/>
+      <c r="J211" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K211" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
@@ -8790,21 +8820,21 @@
       <c r="I212" s="6"/>
       <c r="J212" s="6"/>
       <c r="K212" s="7" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E213" s="5" t="s">
         <v>13</v>
@@ -8815,7 +8845,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="6"/>
       <c r="K213" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8826,13 +8856,13 @@
         <v>11</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F214" s="6"/>
       <c r="G214" s="6"/>
@@ -8840,21 +8870,21 @@
       <c r="I214" s="6"/>
       <c r="J214" s="6"/>
       <c r="K214" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>203</v>
+        <v>2</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E215" s="5" t="s">
         <v>13</v>
@@ -8865,21 +8895,21 @@
       <c r="I215" s="6"/>
       <c r="J215" s="6"/>
       <c r="K215" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E216" s="5" t="s">
         <v>13</v>
@@ -8890,21 +8920,21 @@
       <c r="I216" s="6"/>
       <c r="J216" s="6"/>
       <c r="K216" s="7" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>2045</v>
+        <v>203</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E217" s="5" t="s">
         <v>13</v>
@@ -8915,21 +8945,21 @@
       <c r="I217" s="6"/>
       <c r="J217" s="6"/>
       <c r="K217" s="7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>11</v>
+        <v>251</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E218" s="5" t="s">
         <v>13</v>
@@ -8940,21 +8970,21 @@
       <c r="I218" s="6"/>
       <c r="J218" s="6"/>
       <c r="K218" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>206</v>
+        <v>11</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>2059</v>
+        <v>2045</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>13</v>
@@ -8965,7 +8995,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="6"/>
       <c r="K219" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8976,41 +9006,35 @@
         <v>11</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F220" s="6"/>
-      <c r="G220" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G220" s="6"/>
+      <c r="H220" s="6"/>
       <c r="I220" s="6"/>
-      <c r="J220" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J220" s="6"/>
       <c r="K220" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>11</v>
+        <v>207</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>207</v>
+        <v>2059</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>13</v>
@@ -9021,46 +9045,52 @@
       <c r="I221" s="6"/>
       <c r="J221" s="6"/>
       <c r="K221" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>2083</v>
+        <v>206</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F222" s="6"/>
-      <c r="G222" s="6"/>
-      <c r="H222" s="6"/>
+      <c r="G222" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H222" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I222" s="6"/>
-      <c r="J222" s="6"/>
+      <c r="J222" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K222" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>2092</v>
+        <v>207</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E223" s="5" t="s">
         <v>13</v>
@@ -9071,21 +9101,21 @@
       <c r="I223" s="6"/>
       <c r="J223" s="6"/>
       <c r="K223" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="5" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C224" s="5" t="n">
-        <v>2097</v>
+        <v>2083</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E224" s="5" t="s">
         <v>13</v>
@@ -9096,24 +9126,24 @@
       <c r="I224" s="6"/>
       <c r="J224" s="6"/>
       <c r="K224" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>21</v>
+        <v>2092</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F225" s="6"/>
       <c r="G225" s="6"/>
@@ -9121,21 +9151,21 @@
       <c r="I225" s="6"/>
       <c r="J225" s="6"/>
       <c r="K225" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="5" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E226" s="5" t="s">
         <v>13</v>
@@ -9146,24 +9176,24 @@
       <c r="I226" s="6"/>
       <c r="J226" s="6"/>
       <c r="K226" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B227" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C227" s="5" t="n">
-        <v>2103</v>
-      </c>
       <c r="D227" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F227" s="6"/>
       <c r="G227" s="6"/>
@@ -9171,21 +9201,21 @@
       <c r="I227" s="6"/>
       <c r="J227" s="6"/>
       <c r="K227" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E228" s="5" t="s">
         <v>13</v>
@@ -9196,21 +9226,21 @@
       <c r="I228" s="6"/>
       <c r="J228" s="6"/>
       <c r="K228" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E229" s="5" t="s">
         <v>13</v>
@@ -9221,21 +9251,21 @@
       <c r="I229" s="6"/>
       <c r="J229" s="6"/>
       <c r="K229" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E230" s="5" t="s">
         <v>13</v>
@@ -9246,21 +9276,21 @@
       <c r="I230" s="6"/>
       <c r="J230" s="6"/>
       <c r="K230" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>2112</v>
+        <v>2105</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E231" s="5" t="s">
         <v>13</v>
@@ -9271,21 +9301,21 @@
       <c r="I231" s="6"/>
       <c r="J231" s="6"/>
       <c r="K231" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>2113</v>
+        <v>2106</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E232" s="5" t="s">
         <v>13</v>
@@ -9296,52 +9326,46 @@
       <c r="I232" s="6"/>
       <c r="J232" s="6"/>
       <c r="K232" s="7" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>2120</v>
+        <v>2112</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E233" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F233" s="6"/>
-      <c r="G233" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H233" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G233" s="6"/>
+      <c r="H233" s="6"/>
       <c r="I233" s="6"/>
-      <c r="J233" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J233" s="6"/>
       <c r="K233" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>2125</v>
+        <v>2113</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E234" s="5" t="s">
         <v>13</v>
@@ -9352,7 +9376,7 @@
       <c r="I234" s="6"/>
       <c r="J234" s="6"/>
       <c r="K234" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9363,35 +9387,41 @@
         <v>11</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>2127</v>
+        <v>2120</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F235" s="6"/>
-      <c r="G235" s="6"/>
-      <c r="H235" s="6"/>
+      <c r="G235" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H235" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I235" s="6"/>
-      <c r="J235" s="6"/>
+      <c r="J235" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K235" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="5" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E236" s="5" t="s">
         <v>13</v>
@@ -9402,21 +9432,21 @@
       <c r="I236" s="6"/>
       <c r="J236" s="6"/>
       <c r="K236" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>2137</v>
+        <v>2127</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E237" s="5" t="s">
         <v>13</v>
@@ -9427,21 +9457,21 @@
       <c r="I237" s="6"/>
       <c r="J237" s="6"/>
       <c r="K237" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="5" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>2138</v>
+        <v>2130</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E238" s="5" t="s">
         <v>13</v>
@@ -9452,21 +9482,21 @@
       <c r="I238" s="6"/>
       <c r="J238" s="6"/>
       <c r="K238" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E239" s="5" t="s">
         <v>13</v>
@@ -9477,21 +9507,21 @@
       <c r="I239" s="6"/>
       <c r="J239" s="6"/>
       <c r="K239" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E240" s="5" t="s">
         <v>13</v>
@@ -9502,21 +9532,21 @@
       <c r="I240" s="6"/>
       <c r="J240" s="6"/>
       <c r="K240" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E241" s="5" t="s">
         <v>13</v>
@@ -9527,21 +9557,21 @@
       <c r="I241" s="6"/>
       <c r="J241" s="6"/>
       <c r="K241" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>2158</v>
+        <v>2140</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>13</v>
@@ -9552,21 +9582,21 @@
       <c r="I242" s="6"/>
       <c r="J242" s="6"/>
       <c r="K242" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>2166</v>
+        <v>2141</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>13</v>
@@ -9577,21 +9607,21 @@
       <c r="I243" s="6"/>
       <c r="J243" s="6"/>
       <c r="K243" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="5" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>2190</v>
+        <v>2158</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E244" s="5" t="s">
         <v>13</v>
@@ -9602,52 +9632,46 @@
       <c r="I244" s="6"/>
       <c r="J244" s="6"/>
       <c r="K244" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>22</v>
+        <v>2166</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F245" s="6"/>
-      <c r="G245" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H245" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G245" s="6"/>
+      <c r="H245" s="6"/>
       <c r="I245" s="6"/>
-      <c r="J245" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J245" s="6"/>
       <c r="K245" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>2204</v>
+        <v>2190</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E246" s="5" t="s">
         <v>13</v>
@@ -9658,123 +9682,121 @@
       <c r="I246" s="6"/>
       <c r="J246" s="6"/>
       <c r="K246" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>264</v>
+        <v>11</v>
       </c>
       <c r="C247" s="5" t="n">
-        <v>2211</v>
+        <v>22</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F247" s="6"/>
-      <c r="G247" s="6"/>
-      <c r="H247" s="6"/>
+      <c r="G247" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H247" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I247" s="6"/>
-      <c r="J247" s="6"/>
+      <c r="J247" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K247" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="5" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>564</v>
+        <v>251</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>224</v>
+        <v>2204</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F248" s="6"/>
-      <c r="G248" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="H248" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I248" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="J248" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="G248" s="6"/>
+      <c r="H248" s="6"/>
+      <c r="I248" s="6"/>
+      <c r="J248" s="6"/>
       <c r="K248" s="7" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>11</v>
+        <v>265</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>2241</v>
+        <v>2211</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F249" s="6"/>
-      <c r="G249" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="H249" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G249" s="6"/>
+      <c r="H249" s="6"/>
       <c r="I249" s="6"/>
-      <c r="J249" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J249" s="6"/>
       <c r="K249" s="7" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="E250" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F250" s="6"/>
-      <c r="G250" s="6"/>
-      <c r="H250" s="6"/>
-      <c r="I250" s="6"/>
+      <c r="G250" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="H250" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I250" s="6" t="s">
+        <v>568</v>
+      </c>
       <c r="J250" s="6" t="s">
-        <v>573</v>
+        <v>44</v>
       </c>
       <c r="K250" s="7" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9785,63 +9807,71 @@
         <v>11</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>23</v>
+        <v>2241</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F251" s="6"/>
-      <c r="G251" s="6"/>
-      <c r="H251" s="6"/>
+      <c r="G251" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="H251" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I251" s="6"/>
-      <c r="J251" s="6"/>
+      <c r="J251" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K251" s="7" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="5" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>176</v>
+        <v>572</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F252" s="6"/>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
       <c r="I252" s="6"/>
-      <c r="J252" s="6"/>
+      <c r="J252" s="6" t="s">
+        <v>574</v>
+      </c>
       <c r="K252" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>232</v>
+        <v>23</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F253" s="6"/>
       <c r="G253" s="6"/>
@@ -9849,24 +9879,24 @@
       <c r="I253" s="6"/>
       <c r="J253" s="6"/>
       <c r="K253" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="5" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>581</v>
+        <v>177</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="E254" s="8" t="s">
-        <v>41</v>
+        <v>578</v>
+      </c>
+      <c r="E254" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="F254" s="6"/>
       <c r="G254" s="6"/>
@@ -9874,24 +9904,24 @@
       <c r="I254" s="6"/>
       <c r="J254" s="6"/>
       <c r="K254" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>11</v>
+        <v>177</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>25</v>
+        <v>232</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="F255" s="6"/>
       <c r="G255" s="6"/>
@@ -9899,24 +9929,24 @@
       <c r="I255" s="6"/>
       <c r="J255" s="6"/>
       <c r="K255" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="5" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>11</v>
+        <v>582</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F256" s="6"/>
       <c r="G256" s="6"/>
@@ -9924,7 +9954,7 @@
       <c r="I256" s="6"/>
       <c r="J256" s="6"/>
       <c r="K256" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9935,13 +9965,13 @@
         <v>11</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F257" s="6"/>
       <c r="G257" s="6"/>
@@ -9949,7 +9979,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="6"/>
       <c r="K257" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9960,10 +9990,10 @@
         <v>11</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E258" s="5" t="s">
         <v>13</v>
@@ -9974,21 +10004,21 @@
       <c r="I258" s="6"/>
       <c r="J258" s="6"/>
       <c r="K258" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>3104</v>
+        <v>29</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E259" s="5" t="s">
         <v>13</v>
@@ -9999,21 +10029,21 @@
       <c r="I259" s="6"/>
       <c r="J259" s="6"/>
       <c r="K259" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>3106</v>
+        <v>3</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>13</v>
@@ -10024,21 +10054,21 @@
       <c r="I260" s="6"/>
       <c r="J260" s="6"/>
       <c r="K260" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>33</v>
+        <v>3104</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E261" s="5" t="s">
         <v>13</v>
@@ -10049,21 +10079,21 @@
       <c r="I261" s="6"/>
       <c r="J261" s="6"/>
       <c r="K261" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="5" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>597</v>
+        <v>46</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>333</v>
+        <v>3106</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>13</v>
@@ -10074,7 +10104,7 @@
       <c r="I262" s="6"/>
       <c r="J262" s="6"/>
       <c r="K262" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10085,10 +10115,10 @@
         <v>11</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E263" s="5" t="s">
         <v>13</v>
@@ -10099,21 +10129,21 @@
       <c r="I263" s="6"/>
       <c r="J263" s="6"/>
       <c r="K263" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="5" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>11</v>
+        <v>598</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>4</v>
+        <v>333</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E264" s="5" t="s">
         <v>13</v>
@@ -10124,7 +10154,7 @@
       <c r="I264" s="6"/>
       <c r="J264" s="6"/>
       <c r="K264" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10135,10 +10165,10 @@
         <v>11</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E265" s="5" t="s">
         <v>13</v>
@@ -10149,7 +10179,7 @@
       <c r="I265" s="6"/>
       <c r="J265" s="6"/>
       <c r="K265" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10160,10 +10190,10 @@
         <v>11</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E266" s="5" t="s">
         <v>13</v>
@@ -10174,7 +10204,7 @@
       <c r="I266" s="6"/>
       <c r="J266" s="6"/>
       <c r="K266" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10185,13 +10215,13 @@
         <v>11</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F267" s="6"/>
       <c r="G267" s="6"/>
@@ -10199,7 +10229,7 @@
       <c r="I267" s="6"/>
       <c r="J267" s="6"/>
       <c r="K267" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10210,10 +10240,10 @@
         <v>11</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E268" s="5" t="s">
         <v>13</v>
@@ -10224,7 +10254,7 @@
       <c r="I268" s="6"/>
       <c r="J268" s="6"/>
       <c r="K268" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10235,13 +10265,13 @@
         <v>11</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F269" s="6"/>
       <c r="G269" s="6"/>
@@ -10249,7 +10279,7 @@
       <c r="I269" s="6"/>
       <c r="J269" s="6"/>
       <c r="K269" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10260,10 +10290,10 @@
         <v>11</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E270" s="5" t="s">
         <v>13</v>
@@ -10274,7 +10304,7 @@
       <c r="I270" s="6"/>
       <c r="J270" s="6"/>
       <c r="K270" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10285,27 +10315,21 @@
         <v>11</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F271" s="6"/>
-      <c r="G271" s="6" t="s">
-        <v>616</v>
-      </c>
-      <c r="H271" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G271" s="6"/>
+      <c r="H271" s="6"/>
       <c r="I271" s="6"/>
-      <c r="J271" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J271" s="6"/>
       <c r="K271" s="7" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10316,52 +10340,52 @@
         <v>11</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F272" s="6"/>
-      <c r="G272" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H272" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G272" s="6"/>
+      <c r="H272" s="6"/>
       <c r="I272" s="6"/>
-      <c r="J272" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J272" s="6"/>
       <c r="K272" s="7" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>206</v>
+        <v>11</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F273" s="6"/>
-      <c r="G273" s="6"/>
-      <c r="H273" s="6"/>
+      <c r="G273" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="H273" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I273" s="6"/>
-      <c r="J273" s="6"/>
+      <c r="J273" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K273" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10372,35 +10396,41 @@
         <v>11</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F274" s="6"/>
-      <c r="G274" s="6"/>
-      <c r="H274" s="6"/>
+      <c r="G274" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H274" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I274" s="6"/>
-      <c r="J274" s="6"/>
+      <c r="J274" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K274" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>13</v>
@@ -10411,7 +10441,7 @@
       <c r="I275" s="6"/>
       <c r="J275" s="6"/>
       <c r="K275" s="7" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10422,83 +10452,77 @@
         <v>11</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F276" s="6"/>
-      <c r="G276" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H276" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G276" s="6"/>
+      <c r="H276" s="6"/>
       <c r="I276" s="6"/>
-      <c r="J276" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J276" s="6"/>
       <c r="K276" s="7" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>627</v>
+        <v>600</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F277" s="6"/>
-      <c r="G277" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H277" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G277" s="6"/>
+      <c r="H277" s="6"/>
       <c r="I277" s="6"/>
-      <c r="J277" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J277" s="6"/>
       <c r="K277" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>629</v>
+        <v>11</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F278" s="6"/>
-      <c r="G278" s="6"/>
-      <c r="H278" s="6"/>
+      <c r="G278" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H278" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I278" s="6"/>
-      <c r="J278" s="6"/>
+      <c r="J278" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K278" s="7" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10509,13 +10533,13 @@
         <v>11</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F279" s="6"/>
       <c r="G279" s="6" t="s">
@@ -10529,21 +10553,21 @@
         <v>44</v>
       </c>
       <c r="K279" s="7" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>206</v>
+        <v>630</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E280" s="5" t="s">
         <v>13</v>
@@ -10554,7 +10578,7 @@
       <c r="I280" s="6"/>
       <c r="J280" s="6"/>
       <c r="K280" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10565,35 +10589,41 @@
         <v>11</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E281" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F281" s="6"/>
-      <c r="G281" s="6"/>
-      <c r="H281" s="6"/>
+      <c r="G281" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H281" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I281" s="6"/>
-      <c r="J281" s="6"/>
+      <c r="J281" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K281" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>638</v>
+        <v>207</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>13</v>
@@ -10604,21 +10634,21 @@
       <c r="I282" s="6"/>
       <c r="J282" s="6"/>
       <c r="K282" s="7" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>641</v>
+        <v>11</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>13</v>
@@ -10629,24 +10659,24 @@
       <c r="I283" s="6"/>
       <c r="J283" s="6"/>
       <c r="K283" s="7" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>11</v>
+        <v>639</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F284" s="6"/>
       <c r="G284" s="6"/>
@@ -10654,38 +10684,32 @@
       <c r="I284" s="6"/>
       <c r="J284" s="6"/>
       <c r="K284" s="7" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>11</v>
+        <v>642</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F285" s="6"/>
-      <c r="G285" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H285" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G285" s="6"/>
+      <c r="H285" s="6"/>
       <c r="I285" s="6"/>
-      <c r="J285" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J285" s="6"/>
       <c r="K285" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10696,27 +10720,21 @@
         <v>11</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E286" s="5" t="s">
         <v>41</v>
       </c>
       <c r="F286" s="6"/>
-      <c r="G286" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H286" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G286" s="6"/>
+      <c r="H286" s="6"/>
       <c r="I286" s="6"/>
-      <c r="J286" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J286" s="6"/>
       <c r="K286" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10727,10 +10745,10 @@
         <v>11</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>41</v>
@@ -10747,7 +10765,7 @@
         <v>44</v>
       </c>
       <c r="K287" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10758,10 +10776,10 @@
         <v>11</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E288" s="5" t="s">
         <v>41</v>
@@ -10778,7 +10796,7 @@
         <v>44</v>
       </c>
       <c r="K288" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10789,21 +10807,27 @@
         <v>11</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F289" s="6"/>
-      <c r="G289" s="6"/>
-      <c r="H289" s="6"/>
+      <c r="G289" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H289" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I289" s="6"/>
-      <c r="J289" s="6"/>
+      <c r="J289" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K289" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10814,10 +10838,10 @@
         <v>11</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E290" s="5" t="s">
         <v>41</v>
@@ -10834,7 +10858,7 @@
         <v>44</v>
       </c>
       <c r="K290" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10845,13 +10869,13 @@
         <v>11</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F291" s="6"/>
       <c r="G291" s="6"/>
@@ -10859,49 +10883,55 @@
       <c r="I291" s="6"/>
       <c r="J291" s="6"/>
       <c r="K291" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F292" s="6"/>
-      <c r="G292" s="6"/>
-      <c r="H292" s="6"/>
+      <c r="G292" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H292" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I292" s="6"/>
-      <c r="J292" s="6"/>
+      <c r="J292" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K292" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>662</v>
+        <v>11</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F293" s="6"/>
       <c r="G293" s="6"/>
@@ -10909,55 +10939,49 @@
       <c r="I293" s="6"/>
       <c r="J293" s="6"/>
       <c r="K293" s="7" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F294" s="6"/>
-      <c r="G294" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H294" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G294" s="6"/>
+      <c r="H294" s="6"/>
       <c r="I294" s="6"/>
-      <c r="J294" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J294" s="6"/>
       <c r="K294" s="7" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>11</v>
+        <v>663</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F295" s="6"/>
       <c r="G295" s="6"/>
@@ -10965,7 +10989,7 @@
       <c r="I295" s="6"/>
       <c r="J295" s="6"/>
       <c r="K295" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10976,10 +11000,10 @@
         <v>11</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E296" s="5" t="s">
         <v>41</v>
@@ -10996,7 +11020,7 @@
         <v>44</v>
       </c>
       <c r="K296" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11007,13 +11031,13 @@
         <v>11</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F297" s="6"/>
       <c r="G297" s="6"/>
@@ -11021,46 +11045,52 @@
       <c r="I297" s="6"/>
       <c r="J297" s="6"/>
       <c r="K297" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>673</v>
+        <v>11</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E298" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F298" s="6"/>
-      <c r="G298" s="6"/>
-      <c r="H298" s="6"/>
+      <c r="G298" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H298" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I298" s="6"/>
-      <c r="J298" s="6"/>
+      <c r="J298" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K298" s="7" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="E299" s="5" t="s">
         <v>13</v>
@@ -11071,21 +11101,21 @@
       <c r="I299" s="6"/>
       <c r="J299" s="6"/>
       <c r="K299" s="7" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E300" s="5" t="s">
         <v>13</v>
@@ -11096,21 +11126,21 @@
       <c r="I300" s="6"/>
       <c r="J300" s="6"/>
       <c r="K300" s="7" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="5" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E301" s="5" t="s">
         <v>13</v>
@@ -11121,52 +11151,46 @@
       <c r="I301" s="6"/>
       <c r="J301" s="6"/>
       <c r="K301" s="7" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>11</v>
+        <v>679</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E302" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F302" s="6"/>
-      <c r="G302" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H302" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="G302" s="6"/>
+      <c r="H302" s="6"/>
       <c r="I302" s="6"/>
-      <c r="J302" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="J302" s="6"/>
       <c r="K302" s="7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>9991</v>
+        <v>97</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E303" s="5" t="s">
         <v>13</v>
@@ -11177,7 +11201,7 @@
       <c r="I303" s="6"/>
       <c r="J303" s="6"/>
       <c r="K303" s="7" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11188,21 +11212,27 @@
         <v>11</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F304" s="6"/>
-      <c r="G304" s="6"/>
-      <c r="H304" s="6"/>
+      <c r="G304" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H304" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="I304" s="6"/>
-      <c r="J304" s="6"/>
+      <c r="J304" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="K304" s="7" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11213,10 +11243,10 @@
         <v>11</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>99992</v>
+        <v>9991</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E305" s="5" t="s">
         <v>13</v>
@@ -11227,7 +11257,7 @@
       <c r="I305" s="6"/>
       <c r="J305" s="6"/>
       <c r="K305" s="7" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11238,10 +11268,10 @@
         <v>11</v>
       </c>
       <c r="C306" s="5" t="n">
-        <v>99993</v>
+        <v>9999</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E306" s="5" t="s">
         <v>13</v>
@@ -11252,34 +11282,461 @@
       <c r="I306" s="6"/>
       <c r="J306" s="6"/>
       <c r="K306" s="7" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A307" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C307" s="5" t="n">
+        <v>99992</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="E307" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F307" s="6"/>
+      <c r="G307" s="6"/>
+      <c r="H307" s="6"/>
+      <c r="I307" s="6"/>
+      <c r="J307" s="6"/>
+      <c r="K307" s="7" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A308" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C308" s="5" t="n">
+        <v>99993</v>
+      </c>
+      <c r="D308" s="5" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="9" t="s">
+      <c r="E308" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F308" s="6"/>
+      <c r="G308" s="6"/>
+      <c r="H308" s="6"/>
+      <c r="I308" s="6"/>
+      <c r="J308" s="6"/>
+      <c r="K308" s="7" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="10"/>
-      <c r="B309" s="11" t="s">
+      <c r="A309" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C309" s="5" t="n">
+        <v>3204</v>
+      </c>
+      <c r="D309" s="5" t="s">
         <v>694</v>
       </c>
+      <c r="E309" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K309" s="5" t="n">
+        <v>3204</v>
+      </c>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="12"/>
-      <c r="B310" s="11" t="s">
+      <c r="A310" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B310" s="5" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="311" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="13"/>
-      <c r="B311" s="11" t="s">
+      <c r="C310" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="D310" s="5" t="s">
         <v>696</v>
       </c>
+      <c r="E310" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K310" s="5" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="C311" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="D311" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E311" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="C312" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E312" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K312" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C313" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="E313" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K313" s="5" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C314" s="5" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D314" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E314" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K314" s="5" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="C315" s="5" t="n">
+        <v>99994</v>
+      </c>
+      <c r="D315" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="E315" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K315" s="5" t="n">
+        <v>99994</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="C316" s="5" t="n">
+        <v>4059</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="E316" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K316" s="5" t="n">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="C317" s="5" t="n">
+        <v>1236</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="E317" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K317" s="5" t="n">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="C318" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="D318" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="E318" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K318" s="5" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="C319" s="5" t="n">
+        <v>3103</v>
+      </c>
+      <c r="D319" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="E319" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K319" s="5" t="n">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C320" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="D320" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="E320" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K320" s="5" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="C321" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D321" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E321" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K321" s="5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="C322" s="5" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="E322" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K322" s="5" t="n">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C323" s="5" t="n">
+        <v>2321</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="E323" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="K323" s="5" t="n">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="C324" s="5" t="n">
+        <v>4231</v>
+      </c>
+      <c r="D324" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="E324" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K324" s="5" t="n">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C325" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="D325" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="E325" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K325" s="5" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C326" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="E326" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K326" s="5" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C327" s="5" t="n">
+        <v>4146</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="E327" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K327" s="5" t="n">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C328" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="D328" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="E328" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K328" s="5" t="n">
+        <v>141</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K306"/>
+  <autoFilter ref="A1:K328"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -11304,182 +11761,182 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>697</v>
+        <v>721</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>698</v>
+      <c r="A2" s="8" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>699</v>
+      <c r="A3" s="8" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>700</v>
+      <c r="A4" s="8" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>701</v>
+      <c r="A5" s="8" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>702</v>
+      <c r="A6" s="8" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>703</v>
+      <c r="A7" s="8" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>704</v>
+      <c r="A8" s="8" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>705</v>
+      <c r="A9" s="8" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>706</v>
+      <c r="A10" s="8" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>707</v>
+      <c r="A11" s="8" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>708</v>
+      <c r="A12" s="8" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>709</v>
+      <c r="A13" s="8" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>710</v>
+      <c r="A14" s="8" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>711</v>
+      <c r="A16" s="8" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>712</v>
+      <c r="A17" s="8" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>713</v>
+      <c r="A18" s="8" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>714</v>
+      <c r="A19" s="8" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>715</v>
+      <c r="A20" s="8" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>716</v>
+      <c r="A21" s="8" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>717</v>
+      <c r="A22" s="8" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>718</v>
+      <c r="A23" s="8" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
-        <v>719</v>
+      <c r="A24" s="8" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
-        <v>720</v>
+      <c r="A25" s="8" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>721</v>
+      <c r="A26" s="8" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
-        <v>722</v>
+      <c r="A27" s="8" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
-        <v>723</v>
+      <c r="A28" s="8" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
-        <v>724</v>
+      <c r="A29" s="8" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
-        <v>725</v>
+      <c r="A30" s="8" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
-        <v>726</v>
+      <c r="A31" s="8" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>727</v>
+      <c r="A32" s="8" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>728</v>
+      <c r="A33" s="8" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="8" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
-        <v>729</v>
+      <c r="A35" s="8" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>730</v>
+      <c r="A36" s="8" t="s">
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -11507,123 +11964,123 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>731</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="A1" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>733</v>
+        <v>757</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>734</v>
+        <v>758</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>735</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>736</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>737</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>738</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>739</v>
+      <c r="A3" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>740</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>741</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>742</v>
+      <c r="B4" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>743</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>744</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>745</v>
+      <c r="B5" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>743</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>746</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>747</v>
+      <c r="B6" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>743</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>748</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>749</v>
+      <c r="B7" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>743</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>750</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="B8" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>737</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>751</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>752</v>
+      <c r="B9" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>776</v>
       </c>
     </row>
   </sheetData>
